--- a/dados_excel/tournaments.xlsx
+++ b/dados_excel/tournaments.xlsx
@@ -11,8 +11,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd hh:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -727,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.39999961853027"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1081,6 +1082,32 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Copa LUCE Inters</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AcadArena</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>46271.54166666666</v>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>46333.95833333334</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>assets/tournament-icons/copa_luce.png</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
